--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-05-08 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-05-12 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>361570</v>
+        <v>363740</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2694198.766743977</v>
+        <v>2710368.281150134</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3383382.120825061</v>
+        <v>3403687.840885327</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>241046.6666666667</v>
+        <v>242493.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>267829.6296296296</v>
+        <v>269437.037037037</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3336333.944718501</v>
+        <v>3356357.300251424</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3603240.660295981</v>
+        <v>3624865.884271538</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>266906.7155774804</v>
+        <v>268508.5840201145</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>266906.7155774804</v>
+        <v>268508.5840201145</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.0800000000000001</v>
+        <v>0.08000000000000018</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3615700</v>
+        <v>3637400</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>279366.0552814994</v>
+        <v>281042.6997485766</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>279366.0552814994</v>
+        <v>281042.6997485766</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004435</v>
+        <v>0.08373444023004457</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3568173.453203605</v>
+        <v>3589588.217684762</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>231839.508485104</v>
+        <v>233230.9174333378</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>231839.508485104</v>
+        <v>233230.9174333378</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062554</v>
+        <v>0.06948929943062573</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3415314.47070619</v>
+        <v>3435811.836088916</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>78980.52598768892</v>
+        <v>79454.53583749244</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>78980.52598768892</v>
+        <v>79454.53583749244</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123614</v>
+        <v>0.02367284789123629</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3336333.944718501</v>
+        <v>3356357.300251424</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3336333.944718501</v>
+        <v>3356357.300251424</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3336333.944718501</v>
+        <v>3356357.300251424</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3853627.329459894</v>
+        <v>3876755.275099543</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>517293.3847413929</v>
+        <v>520397.9748481191</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>517293.3847413929</v>
+        <v>520397.9748481191</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850758</v>
+        <v>0.1550484433850759</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2694198.766743977</v>
+        <v>2710368.281150134</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2974971.737878233</v>
+        <v>2992826.340503439</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>280772.9711342561</v>
+        <v>282458.059353305</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>280772.9711342561</v>
+        <v>282458.059353305</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143719</v>
+        <v>0.1042139038143721</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3178015.890001084</v>
+        <v>3197089.083245276</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>483817.1232571071</v>
+        <v>486720.8020951413</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>483817.1232571071</v>
+        <v>486720.8020951413</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466921</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2993554.185271085</v>
+        <v>3011520.312389038</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>299355.4185271082</v>
+        <v>301152.0312389038</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>299355.4185271082</v>
+        <v>301152.0312389038</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.111111111111111</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3233038.520092772</v>
+        <v>3252441.937380161</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>538839.7533487952</v>
+        <v>542073.6562300269</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>538839.7533487952</v>
+        <v>542073.6562300269</v>
       </c>
       <c r="F27" s="44" t="n">
         <v>0.2</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2748179.938451165</v>
+        <v>2764673.426479594</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>53981.17170718824</v>
+        <v>54305.14532945957</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>53981.17170718824</v>
+        <v>54305.14532945957</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984629</v>
+        <v>0.02003607616984633</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2803789.97874423</v>
+        <v>2820617.216219339</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>109591.2120002531</v>
+        <v>110248.9350692043</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>109591.2120002531</v>
+        <v>110248.9350692043</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257622</v>
+        <v>0.04067673601257634</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3305524.153198036</v>
+        <v>3325362.600559377</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>611325.3864540597</v>
+        <v>614994.3194092424</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>611325.3864540597</v>
+        <v>614994.3194092424</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715243</v>
+        <v>0.2269043375715244</v>
       </c>
     </row>
     <row r="31">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3383382.120825061</v>
+        <v>3403687.840885327</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>689183.354081084</v>
+        <v>693319.5597351925</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>689183.354081084</v>
+        <v>693319.5597351925</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693047</v>
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3914892.526954547</v>
+        <v>3938388.16205561</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1220693.76021057</v>
+        <v>1228019.880905476</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1220693.76021057</v>
+        <v>1228019.880905476</v>
       </c>
       <c r="F32" s="44" t="n">
         <v>0.4530822949213272</v>

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-05-12 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-05-17 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>363740</v>
+        <v>370681</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2710368.281150134</v>
+        <v>2762088.373082457</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3403687.840885327</v>
+        <v>3468638.072654131</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>242493.3333333333</v>
+        <v>247120.6666666667</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>269437.037037037</v>
+        <v>274578.5185185185</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3356357.300251424</v>
+        <v>3420404.355898438</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3624865.884271538</v>
+        <v>3694036.704370314</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>268508.5840201145</v>
+        <v>273632.3484718753</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>268508.5840201145</v>
+        <v>273632.3484718753</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000018</v>
+        <v>0.08000000000000007</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3637400</v>
+        <v>3706810</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>281042.6997485766</v>
+        <v>286405.6441015615</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>281042.6997485766</v>
+        <v>286405.6441015615</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004457</v>
+        <v>0.08373444023004446</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3589588.217684762</v>
+        <v>3658085.858359281</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>233230.9174333378</v>
+        <v>237681.502460843</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>233230.9174333378</v>
+        <v>237681.502460843</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062573</v>
+        <v>0.06948929943062568</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3435811.836088916</v>
+        <v>3501375.067942144</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>79454.53583749244</v>
+        <v>80970.7120437054</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>79454.53583749244</v>
+        <v>80970.7120437054</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123629</v>
+        <v>0.02367284789123618</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3356357.300251424</v>
+        <v>3420404.355898438</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3356357.300251424</v>
+        <v>3420404.355898438</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3356357.300251424</v>
+        <v>3420404.355898438</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3876755.275099543</v>
+        <v>3950732.727028024</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>520397.9748481191</v>
+        <v>530328.3711295859</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>520397.9748481191</v>
+        <v>530328.3711295859</v>
       </c>
       <c r="F16" s="44" t="n">
         <v>0.1550484433850759</v>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2710368.281150134</v>
+        <v>2762088.373082457</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2992826.340503439</v>
+        <v>3049936.385121667</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>282458.059353305</v>
+        <v>287848.0120392102</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>282458.059353305</v>
+        <v>287848.0120392102</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143721</v>
+        <v>0.1042139038143719</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3197089.083245276</v>
+        <v>3258096.933156766</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>486720.8020951413</v>
+        <v>496008.5600743084</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>486720.8020951413</v>
+        <v>496008.5600743084</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466922</v>
+        <v>0.179577367946692</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>3011520.312389038</v>
+        <v>3068987.08120273</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>301152.0312389038</v>
+        <v>306898.7081202725</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>301152.0312389038</v>
+        <v>306898.7081202725</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1111111111111109</v>
       </c>
     </row>
     <row r="27">
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3252441.937380161</v>
+        <v>3314506.047698949</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>542073.6562300269</v>
+        <v>552417.6746164914</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>542073.6562300269</v>
+        <v>552417.6746164914</v>
       </c>
       <c r="F27" s="44" t="n">
         <v>0.2</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2764673.426479594</v>
+        <v>2817429.786113384</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>54305.14532945957</v>
+        <v>55341.41303092707</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>54305.14532945957</v>
+        <v>55341.41303092707</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984633</v>
+        <v>0.02003607616984634</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2820617.216219339</v>
+        <v>2874441.112677739</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>110248.9350692043</v>
+        <v>112352.7395952814</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>110248.9350692043</v>
+        <v>112352.7395952814</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257634</v>
+        <v>0.04067673601257629</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3325362.600559377</v>
+        <v>3388818.205690741</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>614994.3194092424</v>
+        <v>626729.832608284</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>614994.3194092424</v>
+        <v>626729.832608284</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715244</v>
+        <v>0.2269043375715242</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3403687.840885327</v>
+        <v>3468638.072654131</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>693319.5597351925</v>
+        <v>706549.6995716742</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>693319.5597351925</v>
+        <v>706549.6995716742</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693047</v>
+        <v>0.2558027130693046</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3938388.16205561</v>
+        <v>4013541.711934172</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1228019.880905476</v>
+        <v>1251453.338851715</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1228019.880905476</v>
+        <v>1251453.338851715</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213272</v>
+        <v>0.4530822949213271</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-05-17 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-05-26 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>370681</v>
+        <v>352873</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2762088.373082457</v>
+        <v>2629394.035504182</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3468638.072654131</v>
+        <v>3302000.1635144</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>247120.6666666667</v>
+        <v>235248.6666666667</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>274578.5185185185</v>
+        <v>261387.4074074074</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3420404.355898438</v>
+        <v>3256083.657589544</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3694036.704370314</v>
+        <v>3516570.350196708</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>273632.3484718753</v>
+        <v>260486.6926071639</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>273632.3484718753</v>
+        <v>260486.6926071639</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.08000000000000013</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3706810</v>
+        <v>3528730</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>286405.6441015615</v>
+        <v>272646.3424104559</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>286405.6441015615</v>
+        <v>272646.3424104559</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004446</v>
+        <v>0.08373444023004437</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3658085.858359281</v>
+        <v>3482346.62984295</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>237681.502460843</v>
+        <v>226262.9722534064</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>237681.502460843</v>
+        <v>226262.9722534064</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062568</v>
+        <v>0.0694892994306256</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3501375.067942144</v>
+        <v>3333164.430736802</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>80970.7120437054</v>
+        <v>77080.77314725751</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>80970.7120437054</v>
+        <v>77080.77314725751</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123618</v>
+        <v>0.02367284789123627</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3420404.355898438</v>
+        <v>3256083.657589544</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3420404.355898438</v>
+        <v>3256083.657589544</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3420404.355898438</v>
+        <v>3256083.657589544</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3950732.727028024</v>
+        <v>3760934.360230387</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>530328.3711295859</v>
+        <v>504850.7026408431</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>530328.3711295859</v>
+        <v>504850.7026408431</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850759</v>
+        <v>0.1550484433850758</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2762088.373082457</v>
+        <v>2629394.035504182</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>3049936.385121667</v>
+        <v>2903413.452610299</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>287848.0120392102</v>
+        <v>274019.4171061162</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>287848.0120392102</v>
+        <v>274019.4171061162</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143719</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3258096.933156766</v>
+        <v>3101573.695694755</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>496008.5600743084</v>
+        <v>472179.6601905725</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>496008.5600743084</v>
+        <v>472179.6601905725</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.179577367946692</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>3068987.08120273</v>
+        <v>2921548.928337981</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>306898.7081202725</v>
+        <v>292154.8928337982</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>306898.7081202725</v>
+        <v>292154.8928337982</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111109</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3314506.047698949</v>
+        <v>3155272.842605019</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>552417.6746164914</v>
+        <v>525878.8071008371</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>552417.6746164914</v>
+        <v>525878.8071008371</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2</v>
+        <v>0.2000000000000003</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2817429.786113384</v>
+        <v>2682076.774680084</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>55341.41303092707</v>
+        <v>52682.73917590128</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>55341.41303092707</v>
+        <v>52682.73917590128</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984634</v>
+        <v>0.02003607616984628</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2874441.112677739</v>
+        <v>2736349.202559429</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>112352.7395952814</v>
+        <v>106955.1670552464</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>112352.7395952814</v>
+        <v>106955.1670552464</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257629</v>
+        <v>0.04067673601257635</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3388818.205690741</v>
+        <v>3226014.947344776</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>626729.832608284</v>
+        <v>596620.9118405939</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>626729.832608284</v>
+        <v>596620.9118405939</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715242</v>
+        <v>0.2269043375715245</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3468638.072654131</v>
+        <v>3302000.1635144</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>706549.6995716742</v>
+        <v>672606.1280102176</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>706549.6995716742</v>
+        <v>672606.1280102176</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693046</v>
+        <v>0.2558027130693047</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4013541.711934172</v>
+        <v>3820725.919362867</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1251453.338851715</v>
+        <v>1191331.883858685</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1251453.338851715</v>
+        <v>1191331.883858685</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213271</v>
+        <v>0.4530822949213273</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-05-26 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-06-01 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>352873</v>
+        <v>341687</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2629394.035504182</v>
+        <v>2546042.796726634</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3302000.1635144</v>
+        <v>3197327.451719868</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>235248.6666666667</v>
+        <v>227791.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>261387.4074074074</v>
+        <v>253101.4814814815</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3256083.657589544</v>
+        <v>3152866.489390797</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3516570.350196708</v>
+        <v>3405095.80854206</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>260486.6926071639</v>
+        <v>252229.3191512637</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>260486.6926071639</v>
+        <v>252229.3191512637</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000013</v>
+        <v>0.07999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3528730</v>
+        <v>3416870</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>272646.3424104559</v>
+        <v>264003.5106092039</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>272646.3424104559</v>
+        <v>264003.5106092039</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004437</v>
+        <v>0.08373444023004452</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3482346.62984295</v>
+        <v>3371956.972936859</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>226262.9722534064</v>
+        <v>219090.4835460624</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>226262.9722534064</v>
+        <v>219090.4835460624</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.0694892994306256</v>
+        <v>0.06948929943062558</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3333164.430736802</v>
+        <v>3227503.818215521</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>77080.77314725751</v>
+        <v>74637.32882472407</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>77080.77314725751</v>
+        <v>74637.32882472407</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123627</v>
+        <v>0.02367284789123616</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3256083.657589544</v>
+        <v>3152866.489390797</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3256083.657589544</v>
+        <v>3152866.489390797</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3256083.657589544</v>
+        <v>3152866.489390797</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3760934.360230387</v>
+        <v>3641713.530771808</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>504850.7026408431</v>
+        <v>488847.0413810113</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>504850.7026408431</v>
+        <v>488847.0413810113</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850758</v>
+        <v>0.1550484433850757</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2629394.035504182</v>
+        <v>2546042.796726634</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2903413.452610299</v>
+        <v>2811375.855851979</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>274019.4171061162</v>
+        <v>265333.0591253443</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>274019.4171061162</v>
+        <v>265333.0591253443</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.104213903814372</v>
+        <v>0.1042139038143721</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3101573.695694755</v>
+        <v>3003254.460842439</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>472179.6601905725</v>
+        <v>457211.6641158042</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>472179.6601905725</v>
+        <v>457211.6641158042</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466922</v>
+        <v>0.1795773679466923</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2921548.928337981</v>
+        <v>2828936.440807371</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>292154.8928337982</v>
+        <v>282893.6440807367</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>292154.8928337982</v>
+        <v>282893.6440807367</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.1111111111111109</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3155272.842605019</v>
+        <v>3055251.356071961</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>525878.8071008371</v>
+        <v>509208.5593453264</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>525878.8071008371</v>
+        <v>509208.5593453264</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2000000000000003</v>
+        <v>0.1999999999999998</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2682076.774680084</v>
+        <v>2597055.504133538</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>52682.73917590128</v>
+        <v>51012.70740690362</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>52682.73917590128</v>
+        <v>51012.70740690362</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984628</v>
+        <v>0.02003607616984641</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2736349.202559429</v>
+        <v>2649607.507445805</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>106955.1670552464</v>
+        <v>103564.710719171</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>106955.1670552464</v>
+        <v>103564.710719171</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257635</v>
+        <v>0.04067673601257638</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3226014.947344776</v>
+        <v>3123750.950946643</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>596620.9118405939</v>
+        <v>577708.1542200083</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>596620.9118405939</v>
+        <v>577708.1542200083</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715245</v>
+        <v>0.2269043375715244</v>
       </c>
     </row>
     <row r="31">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3302000.1635144</v>
+        <v>3197327.451719868</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>672606.1280102176</v>
+        <v>651284.6549932333</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>672606.1280102176</v>
+        <v>651284.6549932333</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693047</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3820725.919362867</v>
+        <v>3699609.710035451</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1191331.883858685</v>
+        <v>1153566.913308817</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1191331.883858685</v>
+        <v>1153566.913308817</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213273</v>
+        <v>0.453082294921327</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-06-01 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-06-06 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>341687</v>
+        <v>345908</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2546042.796726634</v>
+        <v>2577495.110232805</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3197327.451719868</v>
+        <v>3236825.352353224</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>227791.3333333333</v>
+        <v>230605.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>253101.4814814815</v>
+        <v>256228.1481481481</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3152866.489390797</v>
+        <v>3191815.145475806</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3405095.80854206</v>
+        <v>3447160.357113871</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>252229.3191512637</v>
+        <v>255345.2116380651</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>252229.3191512637</v>
+        <v>255345.2116380651</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08000000000000018</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3416870</v>
+        <v>3459080</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>264003.5106092039</v>
+        <v>267264.8545241947</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>264003.5106092039</v>
+        <v>267264.8545241947</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004452</v>
+        <v>0.08373444023004453</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3371956.972936859</v>
+        <v>3413612.14384698</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>219090.4835460624</v>
+        <v>221796.9983711741</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>219090.4835460624</v>
+        <v>221796.9983711741</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062558</v>
+        <v>0.06948929943062561</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3227503.818215521</v>
+        <v>3267374.499911598</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>74637.32882472407</v>
+        <v>75559.35443579266</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>74637.32882472407</v>
+        <v>75559.35443579266</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123616</v>
+        <v>0.02367284789123619</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3152866.489390797</v>
+        <v>3191815.145475806</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3152866.489390797</v>
+        <v>3191815.145475806</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3152866.489390797</v>
+        <v>3191815.145475806</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3641713.530771808</v>
+        <v>3686701.115354739</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>488847.0413810113</v>
+        <v>494885.9698789334</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>488847.0413810113</v>
+        <v>494885.9698789334</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850757</v>
+        <v>0.155048443385076</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2546042.796726634</v>
+        <v>2577495.110232805</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2811375.855851979</v>
+        <v>2846105.937732621</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>265333.0591253443</v>
+        <v>268610.8274998157</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>265333.0591253443</v>
+        <v>268610.8274998157</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143721</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3003254.460842439</v>
+        <v>3040354.898023882</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>457211.6641158042</v>
+        <v>462859.7877910766</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>457211.6641158042</v>
+        <v>462859.7877910766</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466923</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2828936.440807371</v>
+        <v>2863883.455814228</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>282893.6440807367</v>
+        <v>286388.3455814226</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>282893.6440807367</v>
+        <v>286388.3455814226</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111109</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3055251.356071961</v>
+        <v>3092994.132279367</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>509208.5593453264</v>
+        <v>515499.0220465614</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>509208.5593453264</v>
+        <v>515499.0220465614</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.1999999999999998</v>
+        <v>0.2000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2597055.504133538</v>
+        <v>2629137.998588836</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51012.70740690362</v>
+        <v>51642.88835603092</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51012.70740690362</v>
+        <v>51642.88835603092</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984641</v>
+        <v>0.02003607616984632</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2649607.507445805</v>
+        <v>2682339.198405452</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>103564.710719171</v>
+        <v>104844.0881726462</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>103564.710719171</v>
+        <v>104844.0881726462</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257638</v>
+        <v>0.04067673601257636</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3123750.950946643</v>
+        <v>3162339.930814023</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>577708.1542200083</v>
+        <v>584844.8205812178</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>577708.1542200083</v>
+        <v>584844.8205812178</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715244</v>
+        <v>0.2269043375715243</v>
       </c>
     </row>
     <row r="31">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3197327.451719868</v>
+        <v>3236825.352353224</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>651284.6549932333</v>
+        <v>659330.2421204182</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>651284.6549932333</v>
+        <v>659330.2421204182</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693047</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3699609.710035451</v>
+        <v>3745312.509925584</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1153566.913308817</v>
+        <v>1167817.399692779</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1153566.913308817</v>
+        <v>1167817.399692779</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.453082294921327</v>
+        <v>0.4530822949213273</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-06-06 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-06-12 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>345908</v>
+        <v>341797</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2577495.110232805</v>
+        <v>2546862.449530633</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3236825.352353224</v>
+        <v>3198356.773934904</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>230605.3333333333</v>
+        <v>227864.6666666666</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>256228.1481481481</v>
+        <v>253182.9629629629</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3191815.145475806</v>
+        <v>3153881.498196613</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3447160.357113871</v>
+        <v>3406192.018052342</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>255345.2116380651</v>
+        <v>252310.5198557288</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>255345.2116380651</v>
+        <v>252310.5198557288</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000018</v>
+        <v>0.07999999999999993</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3459080</v>
+        <v>3417970</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>267264.8545241947</v>
+        <v>264088.501803387</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>267264.8545241947</v>
+        <v>264088.501803387</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004453</v>
+        <v>0.08373444023004432</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3413612.14384698</v>
+        <v>3373042.513993508</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>221796.9983711741</v>
+        <v>219161.0157968947</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>221796.9983711741</v>
+        <v>219161.0157968947</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062561</v>
+        <v>0.06948929943062565</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3267374.499911598</v>
+        <v>3228542.855170405</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>75559.35443579266</v>
+        <v>74661.35697379243</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>75559.35443579266</v>
+        <v>74661.35697379243</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123619</v>
+        <v>0.02367284789123616</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3191815.145475806</v>
+        <v>3153881.498196613</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3191815.145475806</v>
+        <v>3153881.498196613</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3191815.145475806</v>
+        <v>3153881.498196613</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3686701.115354739</v>
+        <v>3642885.915112988</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>494885.9698789334</v>
+        <v>489004.416916375</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>494885.9698789334</v>
+        <v>489004.416916375</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.155048443385076</v>
+        <v>0.1550484433850756</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2577495.110232805</v>
+        <v>2546862.449530633</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2846105.937732621</v>
+        <v>2812280.927874454</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>268610.8274998157</v>
+        <v>265418.4783438216</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>268610.8274998157</v>
+        <v>265418.4783438216</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.104213903814372</v>
+        <v>0.1042139038143721</v>
       </c>
     </row>
     <row r="25">
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3040354.898023882</v>
+        <v>3004221.304739609</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>462859.7877910766</v>
+        <v>457358.8552089762</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>462859.7877910766</v>
+        <v>457358.8552089762</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>0.1795773679466922</v>
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2863883.455814228</v>
+        <v>2829847.166145148</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>286388.3455814226</v>
+        <v>282984.7166145151</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>286388.3455814226</v>
+        <v>282984.7166145151</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.111111111111111</v>
+        <v>0.1111111111111112</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3092994.132279367</v>
+        <v>3056234.939436759</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>515499.0220465614</v>
+        <v>509372.4899061266</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>515499.0220465614</v>
+        <v>509372.4899061266</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2000000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2629137.998588836</v>
+        <v>2597891.57956355</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51642.88835603092</v>
+        <v>51029.13003291748</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51642.88835603092</v>
+        <v>51029.13003291748</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984632</v>
+        <v>0.02003607616984646</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2682339.198405452</v>
+        <v>2650460.501050534</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>104844.0881726462</v>
+        <v>103598.051519901</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>104844.0881726462</v>
+        <v>103598.051519901</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257636</v>
+        <v>0.04067673601257632</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3162339.930814023</v>
+        <v>3124756.586527171</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>584844.8205812178</v>
+        <v>577894.1369965384</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>584844.8205812178</v>
+        <v>577894.1369965384</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715243</v>
+        <v>0.2269043375715245</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3236825.352353224</v>
+        <v>3198356.773934904</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>659330.2421204182</v>
+        <v>651494.3244042713</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>659330.2421204182</v>
+        <v>651494.3244042713</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693047</v>
+        <v>0.2558027130693049</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3745312.509925584</v>
+        <v>3700800.733012924</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1167817.399692779</v>
+        <v>1153938.283482292</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1167817.399692779</v>
+        <v>1153938.283482292</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213273</v>
+        <v>0.4530822949213271</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-06-12 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-06-19 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>341797</v>
+        <v>344162</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2546862.449530633</v>
+        <v>2564484.984816607</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3198356.773934904</v>
+        <v>3220487.201558189</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>227864.6666666666</v>
+        <v>229441.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>253182.9629629629</v>
+        <v>254934.8148148148</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3153881.498196613</v>
+        <v>3175704.187521665</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3406192.018052342</v>
+        <v>3429760.522523399</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>252310.5198557288</v>
+        <v>254056.3350017332</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>252310.5198557288</v>
+        <v>254056.3350017332</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.07999999999999993</v>
+        <v>0.07999999999999997</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3417970</v>
+        <v>3441620</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>264088.501803387</v>
+        <v>265915.8124783351</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>264088.501803387</v>
+        <v>265915.8124783351</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004432</v>
+        <v>0.08373444023004456</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3373042.513993508</v>
+        <v>3396381.64671145</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>219161.0157968947</v>
+        <v>220677.4591897847</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>219161.0157968947</v>
+        <v>220677.4591897847</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062565</v>
+        <v>0.06948929943062564</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3228542.855170405</v>
+        <v>3250882.149700428</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>74661.35697379243</v>
+        <v>75177.96217876254</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>74661.35697379243</v>
+        <v>75177.96217876254</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123616</v>
+        <v>0.0236728478912363</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3153881.498196613</v>
+        <v>3175704.187521665</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3153881.498196613</v>
+        <v>3175704.187521665</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3153881.498196613</v>
+        <v>3175704.187521665</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3642885.915112988</v>
+        <v>3668092.178448366</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>489004.416916375</v>
+        <v>492387.9909267006</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>489004.416916375</v>
+        <v>492387.9909267006</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850756</v>
+        <v>0.1550484433850757</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2546862.449530633</v>
+        <v>2564484.984816607</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2812280.927874454</v>
+        <v>2831739.976357686</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>265418.4783438216</v>
+        <v>267254.9915410792</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>265418.4783438216</v>
+        <v>267254.9915410792</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>0.1042139038143721</v>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3004221.304739609</v>
+        <v>3025008.448528786</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>457358.8552089762</v>
+        <v>460523.4637121791</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>457358.8552089762</v>
+        <v>460523.4637121791</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>0.1795773679466922</v>
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2829847.166145148</v>
+        <v>2849427.760907341</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>282984.7166145151</v>
+        <v>284942.7760907342</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>282984.7166145151</v>
+        <v>284942.7760907342</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3056234.939436759</v>
+        <v>3077381.981779928</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>509372.4899061266</v>
+        <v>512896.9969633212</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>509372.4899061266</v>
+        <v>512896.9969633212</v>
       </c>
       <c r="F27" s="44" t="n">
         <v>0.2</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2597891.57956355</v>
+        <v>2615867.201308819</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51029.13003291748</v>
+        <v>51382.21649221284</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51029.13003291748</v>
+        <v>51382.21649221284</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984646</v>
+        <v>0.02003607616984637</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2650460.501050534</v>
+        <v>2668799.863552208</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>103598.051519901</v>
+        <v>104314.878735601</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>103598.051519901</v>
+        <v>104314.878735601</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257632</v>
+        <v>0.04067673601257635</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3124756.586527171</v>
+        <v>3146377.75150854</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>577894.1369965384</v>
+        <v>581892.7666919329</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>577894.1369965384</v>
+        <v>581892.7666919329</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715245</v>
+        <v>0.2269043375715244</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3198356.773934904</v>
+        <v>3220487.201558189</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>651494.3244042713</v>
+        <v>656002.2167415828</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>651494.3244042713</v>
+        <v>656002.2167415828</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693049</v>
+        <v>0.2558027130693048</v>
       </c>
     </row>
     <row r="32">
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3700800.733012924</v>
+        <v>3726407.727028599</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1153938.283482292</v>
+        <v>1161922.742211993</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1153938.283482292</v>
+        <v>1161922.742211993</v>
       </c>
       <c r="F32" s="44" t="n">
         <v>0.4530822949213271</v>

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-06-19 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-06-23 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>344162</v>
+        <v>342660</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2564484.984816607</v>
+        <v>2553292.99834746</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3220487.201558189</v>
+        <v>3206432.2745856</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>229441.3333333333</v>
+        <v>228440</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>254934.8148148148</v>
+        <v>253822.2222222222</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3175704.187521665</v>
+        <v>3161844.703645882</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3429760.522523399</v>
+        <v>3414792.279937552</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>254056.3350017332</v>
+        <v>252947.5762916706</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>254056.3350017332</v>
+        <v>252947.5762916706</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.07999999999999997</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3441620</v>
+        <v>3426600</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>265915.8124783351</v>
+        <v>264755.2963541183</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>265915.8124783351</v>
+        <v>264755.2963541183</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004456</v>
+        <v>0.08373444023004431</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3396381.64671145</v>
+        <v>3381559.077010668</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>220677.4591897847</v>
+        <v>219714.3733647866</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>220677.4591897847</v>
+        <v>219714.3733647866</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062564</v>
+        <v>0.06948929943062569</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3250882.149700428</v>
+        <v>3236694.572371001</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>75177.96217876254</v>
+        <v>74849.86872511962</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>75177.96217876254</v>
+        <v>74849.86872511962</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.0236728478912363</v>
+        <v>0.02367284789123616</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3175704.187521665</v>
+        <v>3161844.703645882</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3175704.187521665</v>
+        <v>3161844.703645882</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3175704.187521665</v>
+        <v>3161844.703645882</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3668092.178448366</v>
+        <v>3652083.803171522</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>492387.9909267006</v>
+        <v>490239.0995256398</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>492387.9909267006</v>
+        <v>490239.0995256398</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850757</v>
+        <v>0.1550484433850756</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2564484.984816607</v>
+        <v>2553292.99834746</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2831739.976357686</v>
+        <v>2819381.629287152</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>267254.9915410792</v>
+        <v>266088.6309396918</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>267254.9915410792</v>
+        <v>266088.6309396918</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>0.1042139038143721</v>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3025008.448528786</v>
+        <v>3011806.634587415</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>460523.4637121791</v>
+        <v>458513.6362399547</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>460523.4637121791</v>
+        <v>458513.6362399547</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>0.1795773679466922</v>
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2849427.760907341</v>
+        <v>2836992.220386066</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>284942.7760907342</v>
+        <v>283699.2220386066</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>284942.7760907342</v>
+        <v>283699.2220386066</v>
       </c>
       <c r="F26" s="44" t="n">
         <v>0.1111111111111111</v>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3077381.981779928</v>
+        <v>3063951.598016952</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>512896.9969633212</v>
+        <v>510658.5996694919</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>512896.9969633212</v>
+        <v>510658.5996694919</v>
       </c>
       <c r="F27" s="44" t="n">
         <v>0.2</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2615867.201308819</v>
+        <v>2604450.971346285</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51382.21649221284</v>
+        <v>51157.9729988249</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51382.21649221284</v>
+        <v>51157.9729988249</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984637</v>
+        <v>0.02003607616984628</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2668799.863552208</v>
+        <v>2657152.623603999</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>104314.878735601</v>
+        <v>103859.6252565389</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>104314.878735601</v>
+        <v>103859.6252565389</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257635</v>
+        <v>0.04067673601257623</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3146377.75150854</v>
+        <v>3132646.254763502</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>581892.7666919329</v>
+        <v>579353.2564160419</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>581892.7666919329</v>
+        <v>579353.2564160419</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715244</v>
+        <v>0.2269043375715245</v>
       </c>
     </row>
     <row r="31">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3220487.201558189</v>
+        <v>3206432.2745856</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>656002.2167415828</v>
+        <v>653139.2762381402</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>656002.2167415828</v>
+        <v>653139.2762381402</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693048</v>
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3726407.727028599</v>
+        <v>3710144.849645283</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1161922.742211993</v>
+        <v>1156851.851297823</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1161922.742211993</v>
+        <v>1156851.851297823</v>
       </c>
       <c r="F32" s="44" t="n">
         <v>0.4530822949213271</v>

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-06-23 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-06-30 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>342660</v>
+        <v>337460</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2553292.99834746</v>
+        <v>2514545.7748857</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3206432.2745856</v>
+        <v>3157773.406238419</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>228440</v>
+        <v>224973.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>253822.2222222222</v>
+        <v>249970.3703703704</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3161844.703645882</v>
+        <v>3113862.469189106</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3414792.279937552</v>
+        <v>3362971.466724235</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>252947.5762916706</v>
+        <v>249108.9975351286</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>252947.5762916706</v>
+        <v>249108.9975351286</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000003</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3426600</v>
+        <v>3374600</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>264755.2963541183</v>
+        <v>260737.530810894</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>264755.2963541183</v>
+        <v>260737.530810894</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004431</v>
+        <v>0.08373444023004449</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3381559.077010668</v>
+        <v>3330242.590696376</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>219714.3733647866</v>
+        <v>216380.1215072693</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>219714.3733647866</v>
+        <v>216380.1215072693</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062569</v>
+        <v>0.06948929943062571</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3236694.572371001</v>
+        <v>3187576.461776449</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>74849.86872511962</v>
+        <v>73713.99258734286</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>74849.86872511962</v>
+        <v>73713.99258734286</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123616</v>
+        <v>0.02367284789123619</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3161844.703645882</v>
+        <v>3113862.469189106</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3161844.703645882</v>
+        <v>3113862.469189106</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3161844.703645882</v>
+        <v>3113862.469189106</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3652083.803171522</v>
+        <v>3596661.997952086</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>490239.0995256398</v>
+        <v>482799.5287629794</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>490239.0995256398</v>
+        <v>482799.5287629794</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850756</v>
+        <v>0.1550484433850758</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2553292.99834746</v>
+        <v>2514545.7748857</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2819381.629287152</v>
+        <v>2776596.406406473</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>266088.6309396918</v>
+        <v>262050.6315207737</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>266088.6309396918</v>
+        <v>262050.6315207737</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143721</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3011806.634587415</v>
+        <v>2966101.286721149</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>458513.6362399547</v>
+        <v>451555.5118354494</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>458513.6362399547</v>
+        <v>451555.5118354494</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466922</v>
+        <v>0.1795773679466921</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2836992.220386066</v>
+        <v>2793939.749872999</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>283699.2220386066</v>
+        <v>279393.9749872996</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>283699.2220386066</v>
+        <v>279393.9749872996</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3063951.598016952</v>
+        <v>3017454.929862839</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>510658.5996694919</v>
+        <v>502909.1549771396</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>510658.5996694919</v>
+        <v>502909.1549771396</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2</v>
+        <v>0.1999999999999998</v>
       </c>
     </row>
     <row r="28">
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2604450.971346285</v>
+        <v>2564927.405563875</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51157.9729988249</v>
+        <v>50381.63067817502</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51157.9729988249</v>
+        <v>50381.63067817502</v>
       </c>
       <c r="F28" s="44" t="n">
         <v>0.02003607616984628</v>
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2657152.623603999</v>
+        <v>2616829.289562264</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>103859.6252565389</v>
+        <v>102283.5146765648</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>103859.6252565389</v>
+        <v>102283.5146765648</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257623</v>
+        <v>0.04067673601257635</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3132646.254763502</v>
+        <v>3085107.118229415</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>579353.2564160419</v>
+        <v>570561.3433437152</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>579353.2564160419</v>
+        <v>570561.3433437152</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715245</v>
+        <v>0.2269043375715244</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3206432.2745856</v>
+        <v>3157773.406238419</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>653139.2762381402</v>
+        <v>643227.6313527189</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>653139.2762381402</v>
+        <v>643227.6313527189</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693048</v>
+        <v>0.2558027130693046</v>
       </c>
     </row>
     <row r="32">
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3710144.849645283</v>
+        <v>3653841.945255639</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1156851.851297823</v>
+        <v>1139296.170369939</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1156851.851297823</v>
+        <v>1139296.170369939</v>
       </c>
       <c r="F32" s="44" t="n">
         <v>0.4530822949213271</v>

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>337460</v>
+        <v>330459</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2514545.7748857</v>
+        <v>2462378.599605741</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3157773.406238419</v>
+        <v>3092261.725988685</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>224973.3333333333</v>
+        <v>220306</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>249970.3703703704</v>
+        <v>244784.4444444444</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3113862.469189106</v>
+        <v>3049261.772375283</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3362971.466724235</v>
+        <v>3293202.714165306</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>249108.9975351286</v>
+        <v>243940.9417900229</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>249108.9975351286</v>
+        <v>243940.9417900229</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000003</v>
+        <v>0.08000000000000008</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3374600</v>
+        <v>3304590</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>260737.530810894</v>
+        <v>255328.2276247172</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>260737.530810894</v>
+        <v>255328.2276247172</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004449</v>
+        <v>0.08373444023004434</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3330242.590696376</v>
+        <v>3261152.836718229</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>216380.1215072693</v>
+        <v>211891.0643429463</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>216380.1215072693</v>
+        <v>211891.0643429463</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062571</v>
+        <v>0.06948929943062564</v>
       </c>
     </row>
     <row r="12">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3187576.461776449</v>
+        <v>3121446.482493284</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>73713.99258734286</v>
+        <v>72184.71011800133</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>73713.99258734286</v>
+        <v>72184.71011800133</v>
       </c>
       <c r="F12" s="44" t="n">
         <v>0.02367284789123619</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3113862.469189106</v>
+        <v>3049261.772375283</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3113862.469189106</v>
+        <v>3049261.772375283</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3113862.469189106</v>
+        <v>3049261.772375283</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3596661.997952086</v>
+        <v>3522045.063655687</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>482799.5287629794</v>
+        <v>472783.2912804047</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>482799.5287629794</v>
+        <v>472783.2912804047</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850758</v>
+        <v>0.1550484433850757</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2514545.7748857</v>
+        <v>2462378.599605741</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2776596.406406473</v>
+        <v>2718992.686139622</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>262050.6315207737</v>
+        <v>256614.0865338808</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>262050.6315207737</v>
+        <v>256614.0865338808</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>0.104213903814372</v>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>2966101.286721149</v>
+        <v>2904566.067411202</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>451555.5118354494</v>
+        <v>442187.4678054606</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>451555.5118354494</v>
+        <v>442187.4678054606</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>0.1795773679466921</v>
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2793939.749872999</v>
+        <v>2735976.221784157</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>279393.9749872996</v>
+        <v>273597.6221784158</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>279393.9749872996</v>
+        <v>273597.6221784158</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.111111111111111</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3017454.929862839</v>
+        <v>2954854.319526889</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>502909.1549771396</v>
+        <v>492475.7199211484</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>502909.1549771396</v>
+        <v>492475.7199211484</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.1999999999999998</v>
+        <v>0.2000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2564927.405563875</v>
+        <v>2511715.004786441</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>50381.63067817502</v>
+        <v>49336.40518070012</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>50381.63067817502</v>
+        <v>49336.40518070012</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984628</v>
+        <v>0.02003607616984631</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2616829.289562264</v>
+        <v>2562540.123864921</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>102283.5146765648</v>
+        <v>100161.5242591798</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>102283.5146765648</v>
+        <v>100161.5242591798</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257635</v>
+        <v>0.04067673601257622</v>
       </c>
     </row>
     <row r="30">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3085107.118229415</v>
+        <v>3021102.98459958</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>570561.3433437152</v>
+        <v>558724.3849938386</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>570561.3433437152</v>
+        <v>558724.3849938386</v>
       </c>
       <c r="F30" s="44" t="n">
         <v>0.2269043375715244</v>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3157773.406238419</v>
+        <v>3092261.725988685</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>643227.6313527189</v>
+        <v>629883.1263829437</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>643227.6313527189</v>
+        <v>629883.1263829437</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693046</v>
+        <v>0.2558027130693047</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3653841.945255639</v>
+        <v>3578038.746480274</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1139296.170369939</v>
+        <v>1115660.146874533</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1139296.170369939</v>
+        <v>1115660.146874533</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213271</v>
+        <v>0.4530822949213272</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-06-30 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-07-07 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>330459</v>
+        <v>347853</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2462378.599605741</v>
+        <v>2591988.062085329</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3092261.725988685</v>
+        <v>3255025.640610006</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>220306</v>
+        <v>231902</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>244784.4444444444</v>
+        <v>257668.8888888889</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3049261.772375283</v>
+        <v>3209762.346633196</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3293202.714165306</v>
+        <v>3466543.334363852</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>243940.9417900229</v>
+        <v>256780.9877306558</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>243940.9417900229</v>
+        <v>256780.9877306558</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000008</v>
+        <v>0.08000000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3304590</v>
+        <v>3478530</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>255328.2276247172</v>
+        <v>268767.6533668041</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>255328.2276247172</v>
+        <v>268767.6533668041</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004434</v>
+        <v>0.08373444023004431</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3261152.836718229</v>
+        <v>3432806.483439538</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>211891.0643429463</v>
+        <v>223044.1368063418</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>211891.0643429463</v>
+        <v>223044.1368063418</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062564</v>
+        <v>0.06948929943062566</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3121446.482493284</v>
+        <v>3285746.562432061</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>72184.71011800133</v>
+        <v>75984.21579886507</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>72184.71011800133</v>
+        <v>75984.21579886507</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123619</v>
+        <v>0.02367284789123622</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3049261.772375283</v>
+        <v>3209762.346633196</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3049261.772375283</v>
+        <v>3209762.346633196</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3049261.772375283</v>
+        <v>3209762.346633196</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3522045.063655687</v>
+        <v>3707431.002114701</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>472783.2912804047</v>
+        <v>497668.6554815052</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>472783.2912804047</v>
+        <v>497668.6554815052</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850757</v>
+        <v>0.1550484433850758</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2462378.599605741</v>
+        <v>2591988.062085329</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2718992.686139622</v>
+        <v>2862109.25667549</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>256614.0865338808</v>
+        <v>270121.1945901611</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>256614.0865338808</v>
+        <v>270121.1945901611</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.104213903814372</v>
+        <v>0.1042139038143721</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>2904566.067411202</v>
+        <v>3057450.45602386</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>442187.4678054606</v>
+        <v>465462.3939385312</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>442187.4678054606</v>
+        <v>465462.3939385312</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466921</v>
+        <v>0.1795773679466924</v>
       </c>
     </row>
     <row r="26">
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2735976.221784157</v>
+        <v>2879986.735650366</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>273597.6221784158</v>
+        <v>287998.6735650366</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>273597.6221784158</v>
+        <v>287998.6735650366</v>
       </c>
       <c r="F26" s="44" t="n">
         <v>0.1111111111111111</v>
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>2954854.319526889</v>
+        <v>3110385.674502396</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>492475.7199211484</v>
+        <v>518397.6124170665</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>492475.7199211484</v>
+        <v>518397.6124170665</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2000000000000001</v>
+        <v>0.2000000000000003</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2511715.004786441</v>
+        <v>2643921.332328603</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>49336.40518070012</v>
+        <v>51933.27024327405</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>49336.40518070012</v>
+        <v>51933.27024327405</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984631</v>
+        <v>0.02003607616984633</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2562540.123864921</v>
+        <v>2697421.676234523</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>100161.5242591798</v>
+        <v>105433.6141491942</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>100161.5242591798</v>
+        <v>105433.6141491942</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257622</v>
+        <v>0.04067673601257632</v>
       </c>
     </row>
     <row r="30">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3021102.98459958</v>
+        <v>3180121.3963061</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>558724.3849938386</v>
+        <v>588133.3342207707</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>558724.3849938386</v>
+        <v>588133.3342207707</v>
       </c>
       <c r="F30" s="44" t="n">
         <v>0.2269043375715244</v>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3092261.725988685</v>
+        <v>3255025.640610006</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>629883.1263829437</v>
+        <v>663037.5785246771</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>629883.1263829437</v>
+        <v>663037.5785246771</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693047</v>
+        <v>0.2558027130693049</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3578038.746480274</v>
+        <v>3766371.961663634</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1115660.146874533</v>
+        <v>1174383.899578305</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1115660.146874533</v>
+        <v>1174383.899578305</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213272</v>
+        <v>0.4530822949213274</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>347853</v>
+        <v>331806</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2591988.062085329</v>
+        <v>2472415.620760162</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3255025.640610006</v>
+        <v>3104866.244385541</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>231902</v>
+        <v>221204</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>257668.8888888889</v>
+        <v>245782.2222222222</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3209762.346633196</v>
+        <v>3061691.016570144</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3466543.334363852</v>
+        <v>3306626.297895755</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>256780.9877306558</v>
+        <v>244935.2813256113</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>256780.9877306558</v>
+        <v>244935.2813256113</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000004</v>
+        <v>0.07999999999999993</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3478530</v>
+        <v>3318060</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>268767.6533668041</v>
+        <v>256368.9834298561</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>268767.6533668041</v>
+        <v>256368.9834298561</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004431</v>
+        <v>0.08373444023004425</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3432806.483439538</v>
+        <v>3274445.780384643</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>223044.1368063418</v>
+        <v>212754.7638144991</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>223044.1368063418</v>
+        <v>212754.7638144991</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062566</v>
+        <v>0.06948929943062558</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3285746.562432061</v>
+        <v>3134169.962295373</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>75984.21579886507</v>
+        <v>72478.9457252291</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>75984.21579886507</v>
+        <v>72478.9457252291</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123622</v>
+        <v>0.02367284789123612</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3209762.346633196</v>
+        <v>3061691.016570144</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3209762.346633196</v>
+        <v>3061691.016570144</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3209762.346633196</v>
+        <v>3061691.016570144</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3707431.002114701</v>
+        <v>3536401.442815414</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>497668.6554815052</v>
+        <v>474710.4262452703</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>497668.6554815052</v>
+        <v>474710.4262452703</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850758</v>
+        <v>0.1550484433850755</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2591988.062085329</v>
+        <v>2472415.620760162</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2862109.25667549</v>
+        <v>2730075.704451213</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>270121.1945901611</v>
+        <v>257660.0836910503</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>270121.1945901611</v>
+        <v>257660.0836910503</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143721</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3057450.45602386</v>
+        <v>2916405.510406559</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>465462.3939385312</v>
+        <v>443989.889646397</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>465462.3939385312</v>
+        <v>443989.889646397</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466924</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2879986.735650366</v>
+        <v>2747128.467511292</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>287998.6735650366</v>
+        <v>274712.8467511293</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>287998.6735650366</v>
+        <v>274712.8467511293</v>
       </c>
       <c r="F26" s="44" t="n">
         <v>0.1111111111111111</v>
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3110385.674502396</v>
+        <v>2966898.744912195</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>518397.6124170665</v>
+        <v>494483.1241520322</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>518397.6124170665</v>
+        <v>494483.1241520322</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2000000000000003</v>
+        <v>0.1999999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2643921.332328603</v>
+        <v>2521953.128461231</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51933.27024327405</v>
+        <v>49537.50770106865</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51933.27024327405</v>
+        <v>49537.50770106865</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984633</v>
+        <v>0.02003607616984639</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2697421.676234523</v>
+        <v>2572985.418279193</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>105433.6141491942</v>
+        <v>100569.797519031</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>105433.6141491942</v>
+        <v>100569.797519031</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257632</v>
+        <v>0.04067673601257626</v>
       </c>
     </row>
     <row r="30">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3180121.3963061</v>
+        <v>3033417.449390236</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>588133.3342207707</v>
+        <v>561001.8286300739</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>588133.3342207707</v>
+        <v>561001.8286300739</v>
       </c>
       <c r="F30" s="44" t="n">
         <v>0.2269043375715244</v>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3255025.640610006</v>
+        <v>3104866.244385541</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>663037.5785246771</v>
+        <v>632450.6236253791</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>663037.5785246771</v>
+        <v>632450.6236253791</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693049</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3766371.961663634</v>
+        <v>3592623.364213514</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1174383.899578305</v>
+        <v>1120207.743453352</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1174383.899578305</v>
+        <v>1120207.743453352</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213274</v>
+        <v>0.4530822949213271</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-07-07 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-07-20 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>331806</v>
+        <v>336970</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2472415.620760162</v>
+        <v>2510894.594213341</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3104866.244385541</v>
+        <v>3153188.243644165</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>221204</v>
+        <v>224646.6666666667</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>245782.2222222222</v>
+        <v>249607.4074074074</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3061691.016570144</v>
+        <v>3109341.066326833</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3306626.297895755</v>
+        <v>3358088.35163298</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>244935.2813256113</v>
+        <v>248747.2853061468</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>244935.2813256113</v>
+        <v>248747.2853061468</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.07999999999999993</v>
+        <v>0.08000000000000006</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3318060</v>
+        <v>3369700</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>256368.9834298561</v>
+        <v>260358.9336731667</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>256368.9834298561</v>
+        <v>260358.9336731667</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004425</v>
+        <v>0.08373444023004438</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3274445.780384643</v>
+        <v>3325406.998716759</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>212754.7638144991</v>
+        <v>216065.9323899262</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>212754.7638144991</v>
+        <v>216065.9323899262</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062558</v>
+        <v>0.06948929943062565</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3134169.962295373</v>
+        <v>3182948.024431963</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>72478.9457252291</v>
+        <v>73606.95810512919</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>72478.9457252291</v>
+        <v>73606.95810512919</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123612</v>
+        <v>0.02367284789123617</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3061691.016570144</v>
+        <v>3109341.066326833</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3061691.016570144</v>
+        <v>3109341.066326833</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3061691.016570144</v>
+        <v>3109341.066326833</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3536401.442815414</v>
+        <v>3591439.5586141</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>474710.4262452703</v>
+        <v>482098.492287267</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>474710.4262452703</v>
+        <v>482098.492287267</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850755</v>
+        <v>0.1550484433850757</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2472415.620760162</v>
+        <v>2510894.594213341</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2730075.704451213</v>
+        <v>2772564.721942717</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>257660.0836910503</v>
+        <v>261670.1277293754</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>257660.0836910503</v>
+        <v>261670.1277293754</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.104213903814372</v>
+        <v>0.1042139038143718</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>2916405.510406559</v>
+        <v>2961794.436633751</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>443989.889646397</v>
+        <v>450899.8424204094</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>443989.889646397</v>
+        <v>450899.8424204094</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466922</v>
+        <v>0.1795773679466921</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2747128.467511292</v>
+        <v>2789882.882459268</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>274712.8467511293</v>
+        <v>278988.2882459266</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>274712.8467511293</v>
+        <v>278988.2882459266</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>2966898.744912195</v>
+        <v>3013073.51305601</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>494483.1241520322</v>
+        <v>502178.9188426682</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>494483.1241520322</v>
+        <v>502178.9188426682</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.1999999999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2521953.128461231</v>
+        <v>2561203.069557455</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>49537.50770106865</v>
+        <v>50308.47534411354</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>49537.50770106865</v>
+        <v>50308.47534411354</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984639</v>
+        <v>0.02003607616984619</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2572985.418279193</v>
+        <v>2613029.590777562</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>100569.797519031</v>
+        <v>102134.9965642206</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>100569.797519031</v>
+        <v>102134.9965642206</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257626</v>
+        <v>0.04067673601257617</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3033417.449390236</v>
+        <v>3080627.468825241</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>561001.8286300739</v>
+        <v>569732.8746118993</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>561001.8286300739</v>
+        <v>569732.8746118993</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715244</v>
+        <v>0.2269043375715242</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3104866.244385541</v>
+        <v>3153188.243644165</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>632450.6236253791</v>
+        <v>642293.6494308235</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>632450.6236253791</v>
+        <v>642293.6494308235</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693049</v>
+        <v>0.2558027130693046</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3592623.364213514</v>
+        <v>3648536.479265077</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1120207.743453352</v>
+        <v>1137641.885051735</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1120207.743453352</v>
+        <v>1137641.885051735</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213271</v>
+        <v>0.4530822949213272</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-07-20 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-07-22 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>336970</v>
+        <v>350886</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2510894.594213341</v>
+        <v>2614588.125308314</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3153188.243644165</v>
+        <v>3283406.861320968</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>224646.6666666667</v>
+        <v>233924</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>249607.4074074074</v>
+        <v>259915.5555555556</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3109341.066326833</v>
+        <v>3237748.907615388</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3358088.35163298</v>
+        <v>3496768.820224619</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>248747.2853061468</v>
+        <v>259019.9126092312</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>248747.2853061468</v>
+        <v>259019.9126092312</v>
       </c>
       <c r="F9" s="44" t="n">
         <v>0.08000000000000006</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3369700</v>
+        <v>3508860</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>260358.9336731667</v>
+        <v>271111.0923846122</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>260358.9336731667</v>
+        <v>271111.0923846122</v>
       </c>
       <c r="F10" s="44" t="n">
         <v>0.08373444023004438</v>
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3325406.998716759</v>
+        <v>3462737.810937854</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>216065.9323899262</v>
+        <v>224988.9033224666</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>216065.9323899262</v>
+        <v>224988.9033224666</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062565</v>
+        <v>0.06948929943062561</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3182948.024431963</v>
+        <v>3314395.645015383</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>73606.95810512919</v>
+        <v>76646.73739999533</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>73606.95810512919</v>
+        <v>76646.73739999533</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123617</v>
+        <v>0.02367284789123623</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3109341.066326833</v>
+        <v>3237748.907615388</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3109341.066326833</v>
+        <v>3237748.907615388</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3109341.066326833</v>
+        <v>3237748.907615388</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3591439.5586141</v>
+        <v>3739756.835812883</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>482098.492287267</v>
+        <v>502007.9281974952</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>482098.492287267</v>
+        <v>502007.9281974952</v>
       </c>
       <c r="F16" s="44" t="n">
         <v>0.1550484433850757</v>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2510894.594213341</v>
+        <v>2614588.125308314</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2772564.721942717</v>
+        <v>2887064.560713394</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>261670.1277293754</v>
+        <v>272476.4354050797</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>261670.1277293754</v>
+        <v>272476.4354050797</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143718</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>2961794.436633751</v>
+        <v>3084108.979115857</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>450899.8424204094</v>
+        <v>469520.8538075429</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>450899.8424204094</v>
+        <v>469520.8538075429</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>0.1795773679466921</v>
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2789882.882459268</v>
+        <v>2905097.917009237</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>278988.2882459266</v>
+        <v>290509.7917009233</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>278988.2882459266</v>
+        <v>290509.7917009233</v>
       </c>
       <c r="F26" s="44" t="n">
         <v>0.111111111111111</v>
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3013073.51305601</v>
+        <v>3137505.750369976</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>502178.9188426682</v>
+        <v>522917.6250616624</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>502178.9188426682</v>
+        <v>522917.6250616624</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2</v>
+        <v>0.1999999999999998</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2561203.069557455</v>
+        <v>2666974.212139767</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>50308.47534411354</v>
+        <v>52386.08683145279</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>50308.47534411354</v>
+        <v>52386.08683145279</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984619</v>
+        <v>0.02003607616984621</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2613029.590777562</v>
+        <v>2720941.036263097</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>102134.9965642206</v>
+        <v>106352.9109547827</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>102134.9965642206</v>
+        <v>106352.9109547827</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257617</v>
+        <v>0.04067673601257618</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3080627.468825241</v>
+        <v>3207849.51190377</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>569732.8746118993</v>
+        <v>593261.3865954564</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>569732.8746118993</v>
+        <v>593261.3865954564</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715242</v>
+        <v>0.2269043375715243</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3153188.243644165</v>
+        <v>3283406.861320968</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>642293.6494308235</v>
+        <v>668818.7360126539</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>642293.6494308235</v>
+        <v>668818.7360126539</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693046</v>
+        <v>0.2558027130693047</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3648536.479265077</v>
+        <v>3799211.713397055</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1137641.885051735</v>
+        <v>1184623.588088741</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1137641.885051735</v>
+        <v>1184623.588088741</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213272</v>
+        <v>0.4530822949213271</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>350886</v>
+        <v>367964</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2614588.125308314</v>
+        <v>2741842.948823687</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3283406.861320968</v>
+        <v>3443213.813942729</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>233924</v>
+        <v>245309.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>259915.5555555556</v>
+        <v>272565.9259259259</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3237748.907615388</v>
+        <v>3395333.638394773</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3496768.820224619</v>
+        <v>3666960.329466356</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>259019.9126092312</v>
+        <v>271626.6910715825</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>259019.9126092312</v>
+        <v>271626.6910715825</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000006</v>
+        <v>0.08000000000000018</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3508860</v>
+        <v>3679640</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>271111.0923846122</v>
+        <v>284306.361605227</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>271111.0923846122</v>
+        <v>284306.361605227</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004438</v>
+        <v>0.08373444023004459</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3462737.810937854</v>
+        <v>3631272.994260064</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>224988.9033224666</v>
+        <v>235939.3558652904</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>224988.9033224666</v>
+        <v>235939.3558652904</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062561</v>
+        <v>0.06948929943062575</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3314395.645015383</v>
+        <v>3475710.855156491</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>76646.73739999533</v>
+        <v>80377.21676171711</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>76646.73739999533</v>
+        <v>80377.21676171711</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123623</v>
+        <v>0.02367284789123622</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3237748.907615388</v>
+        <v>3395333.638394773</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3237748.907615388</v>
+        <v>3395333.638394773</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3237748.907615388</v>
+        <v>3395333.638394773</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3739756.835812883</v>
+        <v>3921774.833800869</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>502007.9281974952</v>
+        <v>526441.1954060956</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>502007.9281974952</v>
+        <v>526441.1954060956</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850757</v>
+        <v>0.1550484433850758</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2614588.125308314</v>
+        <v>2741842.948823687</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2887064.560713394</v>
+        <v>3027581.106166513</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>272476.4354050797</v>
+        <v>285738.157342826</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>272476.4354050797</v>
+        <v>285738.157342826</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.104213903814372</v>
+        <v>0.1042139038143721</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3084108.979115857</v>
+        <v>3234215.888896642</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>469520.8538075429</v>
+        <v>492372.9400729551</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>469520.8538075429</v>
+        <v>492372.9400729551</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466921</v>
+        <v>0.1795773679466923</v>
       </c>
     </row>
     <row r="26">
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2905097.917009237</v>
+        <v>3046492.165359652</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>290509.7917009233</v>
+        <v>304649.216535965</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>290509.7917009233</v>
+        <v>304649.216535965</v>
       </c>
       <c r="F26" s="44" t="n">
         <v>0.111111111111111</v>
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3137505.750369976</v>
+        <v>3290211.538588425</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>522917.6250616624</v>
+        <v>548368.5897647375</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>522917.6250616624</v>
+        <v>548368.5897647375</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.1999999999999998</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2666974.212139767</v>
+        <v>2796778.722992075</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>52386.08683145279</v>
+        <v>54935.77416838752</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>52386.08683145279</v>
+        <v>54935.77416838752</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984621</v>
+        <v>0.02003607616984635</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2720941.036263097</v>
+        <v>2853372.170640932</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>106352.9109547827</v>
+        <v>111529.2218172452</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>106352.9109547827</v>
+        <v>111529.2218172452</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257618</v>
+        <v>0.04067673601257644</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3207849.51190377</v>
+        <v>3363979.006851681</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>593261.3865954564</v>
+        <v>622136.0580279939</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>593261.3865954564</v>
+        <v>622136.0580279939</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715243</v>
+        <v>0.2269043375715244</v>
       </c>
     </row>
     <row r="31">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3283406.861320968</v>
+        <v>3443213.813942729</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>668818.7360126539</v>
+        <v>701370.8651190419</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>668818.7360126539</v>
+        <v>701370.8651190419</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693047</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3799211.713397055</v>
+        <v>3984123.444390583</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1184623.588088741</v>
+        <v>1242280.495566896</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1184623.588088741</v>
+        <v>1242280.495566896</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213271</v>
+        <v>0.4530822949213273</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-07-22 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-07-23 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>367964</v>
+        <v>352468</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2741842.948823687</v>
+        <v>2626376.222907641</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3443213.813942729</v>
+        <v>3298210.386268129</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>245309.3333333333</v>
+        <v>234978.6666666667</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>272565.9259259259</v>
+        <v>261087.4074074074</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3395333.638394773</v>
+        <v>3252346.579713583</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3666960.329466356</v>
+        <v>3512534.306090671</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>271626.6910715825</v>
+        <v>260187.7263770872</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>271626.6910715825</v>
+        <v>260187.7263770872</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000018</v>
+        <v>0.08000000000000015</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3679640</v>
+        <v>3524680</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>284306.361605227</v>
+        <v>272333.4202864165</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>284306.361605227</v>
+        <v>272333.4202864165</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004459</v>
+        <v>0.08373444023004445</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3631272.994260064</v>
+        <v>3478349.865043472</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>235939.3558652904</v>
+        <v>226003.2853298886</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>235939.3558652904</v>
+        <v>226003.2853298886</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062575</v>
+        <v>0.06948929943062571</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3475710.855156491</v>
+        <v>3329338.885584726</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>80377.21676171711</v>
+        <v>76992.30587114207</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>80377.21676171711</v>
+        <v>76992.30587114207</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123622</v>
+        <v>0.02367284789123623</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3395333.638394773</v>
+        <v>3252346.579713583</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3395333.638394773</v>
+        <v>3252346.579713583</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3395333.638394773</v>
+        <v>3252346.579713583</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3921774.833800869</v>
+        <v>3756617.85424695</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>526441.1954060956</v>
+        <v>504271.2745333668</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>526441.1954060956</v>
+        <v>504271.2745333668</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850758</v>
+        <v>0.1550484433850759</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2741842.948823687</v>
+        <v>2626376.222907641</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>3027581.106166513</v>
+        <v>2900081.141982092</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>285738.157342826</v>
+        <v>273704.9190744506</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>285738.157342826</v>
+        <v>273704.9190744506</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143721</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3234215.888896642</v>
+        <v>3098013.952255171</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>492372.9400729551</v>
+        <v>471637.7293475294</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>492372.9400729551</v>
+        <v>471637.7293475294</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466923</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>3046492.165359652</v>
+        <v>2918195.803230713</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>304649.216535965</v>
+        <v>291819.5803230712</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>304649.216535965</v>
+        <v>291819.5803230712</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.111111111111111</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3290211.538588425</v>
+        <v>3151651.46748917</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>548368.5897647375</v>
+        <v>525275.2445815285</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>548368.5897647375</v>
+        <v>525275.2445815285</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2</v>
+        <v>0.2000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2796778.722992075</v>
+        <v>2678998.496960492</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>54935.77416838752</v>
+        <v>52622.2740528509</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>54935.77416838752</v>
+        <v>52622.2740528509</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984635</v>
+        <v>0.02003607616984637</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2853372.170640932</v>
+        <v>2733208.635196563</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>111529.2218172452</v>
+        <v>106832.4122889214</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>111529.2218172452</v>
+        <v>106832.4122889214</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257644</v>
+        <v>0.04067673601257631</v>
       </c>
     </row>
     <row r="30">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3363979.006851681</v>
+        <v>3222312.379980102</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>622136.0580279939</v>
+        <v>595936.1570724607</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>622136.0580279939</v>
+        <v>595936.1570724607</v>
       </c>
       <c r="F30" s="44" t="n">
         <v>0.2269043375715244</v>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3443213.813942729</v>
+        <v>3298210.386268129</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>701370.8651190419</v>
+        <v>671834.1633604877</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>701370.8651190419</v>
+        <v>671834.1633604877</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693047</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3984123.444390583</v>
+        <v>3816340.789309443</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1242280.495566896</v>
+        <v>1189964.566401802</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1242280.495566896</v>
+        <v>1189964.566401802</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213273</v>
+        <v>0.4530822949213272</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-07-23 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-08-02 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>352468</v>
+        <v>335340</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2626376.222907641</v>
+        <v>2498748.829935905</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3298210.386268129</v>
+        <v>3137935.55991226</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>234978.6666666667</v>
+        <v>223560</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>261087.4074074074</v>
+        <v>248399.9999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3252346.579713583</v>
+        <v>3094300.48129519</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3512534.306090671</v>
+        <v>3341844.519798806</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>260187.7263770872</v>
+        <v>247544.0385036157</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>260187.7263770872</v>
+        <v>247544.0385036157</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000015</v>
+        <v>0.08000000000000014</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3524680</v>
+        <v>3353400</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>272333.4202864165</v>
+        <v>259099.5187048097</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>272333.4202864165</v>
+        <v>259099.5187048097</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004445</v>
+        <v>0.08373444023004439</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3478349.865043472</v>
+        <v>3309321.253968241</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>226003.2853298886</v>
+        <v>215020.7726730504</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>226003.2853298886</v>
+        <v>215020.7726730504</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062571</v>
+        <v>0.06948929943062561</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3329338.885584726</v>
+        <v>3167551.38591867</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>76992.30587114207</v>
+        <v>73250.90462348005</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>76992.30587114207</v>
+        <v>73250.90462348005</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123623</v>
+        <v>0.02367284789123621</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3252346.579713583</v>
+        <v>3094300.48129519</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3252346.579713583</v>
+        <v>3094300.48129519</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3252346.579713583</v>
+        <v>3094300.48129519</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3756617.85424695</v>
+        <v>3574066.9542857</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>504271.2745333668</v>
+        <v>479766.4729905101</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>504271.2745333668</v>
+        <v>479766.4729905101</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850759</v>
+        <v>0.1550484433850758</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2626376.222907641</v>
+        <v>2498748.829935905</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2900081.141982092</v>
+        <v>2759153.20015512</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>273704.9190744506</v>
+        <v>260404.3702192148</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>273704.9190744506</v>
+        <v>260404.3702192148</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.104213903814372</v>
+        <v>0.1042139038143719</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3098013.952255171</v>
+        <v>2947467.567975671</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>471637.7293475294</v>
+        <v>448718.7380397664</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>471637.7293475294</v>
+        <v>448718.7380397664</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466922</v>
+        <v>0.1795773679466921</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2918195.803230713</v>
+        <v>2776387.588817672</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>291819.5803230712</v>
+        <v>277638.7588817668</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>291819.5803230712</v>
+        <v>277638.7588817668</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3151651.46748917</v>
+        <v>2998498.595923086</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>525275.2445815285</v>
+        <v>499749.7659871806</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>525275.2445815285</v>
+        <v>499749.7659871806</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2000000000000001</v>
+        <v>0.1999999999999998</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2678998.496960492</v>
+        <v>2548813.951821815</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>52622.2740528509</v>
+        <v>50065.12188591016</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>52622.2740528509</v>
+        <v>50065.12188591016</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984637</v>
+        <v>0.02003607616984632</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2733208.635196563</v>
+        <v>2600389.776452941</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>106832.4122889214</v>
+        <v>101640.9465170363</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>106832.4122889214</v>
+        <v>101640.9465170363</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257631</v>
+        <v>0.04067673601257613</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3222312.379980102</v>
+        <v>3065725.777950133</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>595936.1570724607</v>
+        <v>566976.9480142277</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>595936.1570724607</v>
+        <v>566976.9480142277</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715244</v>
+        <v>0.2269043375715242</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3298210.386268129</v>
+        <v>3137935.55991226</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>671834.1633604877</v>
+        <v>639186.7299763546</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>671834.1633604877</v>
+        <v>639186.7299763546</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693047</v>
+        <v>0.2558027130693045</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3816340.789309443</v>
+        <v>3630887.684235245</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1189964.566401802</v>
+        <v>1132138.85429934</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1189964.566401802</v>
+        <v>1132138.85429934</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213272</v>
+        <v>0.453082294921327</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-08-02 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-08-04 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>335340</v>
+        <v>332196</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2498748.829935905</v>
+        <v>2475321.662519794</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3137935.55991226</v>
+        <v>3108515.65951158</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>223560</v>
+        <v>221464</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>248399.9999999999</v>
+        <v>246071.1111111111</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3094300.48129519</v>
+        <v>3065289.684154402</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3341844.519798806</v>
+        <v>3310512.858886754</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>247544.0385036157</v>
+        <v>245223.1747323521</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>247544.0385036157</v>
+        <v>245223.1747323521</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000014</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3353400</v>
+        <v>3321960</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>259099.5187048097</v>
+        <v>256670.3158455985</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>259099.5187048097</v>
+        <v>256670.3158455985</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004439</v>
+        <v>0.08373444023004442</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3309321.253968241</v>
+        <v>3278294.516858215</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>215020.7726730504</v>
+        <v>213004.8327038134</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>215020.7726730504</v>
+        <v>213004.8327038134</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062561</v>
+        <v>0.06948929943062575</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3167551.38591867</v>
+        <v>3137853.820589964</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>73250.90462348005</v>
+        <v>72564.13643556274</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>73250.90462348005</v>
+        <v>72564.13643556274</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123621</v>
+        <v>0.02367284789123625</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3094300.48129519</v>
+        <v>3065289.684154402</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3094300.48129519</v>
+        <v>3065289.684154402</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3094300.48129519</v>
+        <v>3065289.684154402</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3574066.9542857</v>
+        <v>3540558.078206872</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>479766.4729905101</v>
+        <v>475268.3940524706</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>479766.4729905101</v>
+        <v>475268.3940524706</v>
       </c>
       <c r="F16" s="44" t="n">
         <v>0.1550484433850758</v>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2498748.829935905</v>
+        <v>2475321.662519794</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2759153.20015512</v>
+        <v>2733284.596167264</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>260404.3702192148</v>
+        <v>257962.9336474692</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>260404.3702192148</v>
+        <v>257962.9336474692</v>
       </c>
       <c r="F24" s="44" t="n">
-        <v>0.1042139038143719</v>
+        <v>0.104213903814372</v>
       </c>
     </row>
     <row r="25">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>2947467.567975671</v>
+        <v>2919833.411496529</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>448718.7380397664</v>
+        <v>444511.7489767349</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>448718.7380397664</v>
+        <v>444511.7489767349</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466921</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2776387.588817672</v>
+        <v>2750357.402799771</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>277638.7588817668</v>
+        <v>275035.7402799767</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>277638.7588817668</v>
+        <v>275035.7402799767</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.111111111111111</v>
+        <v>0.1111111111111109</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>2998498.595923086</v>
+        <v>2970385.995023753</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>499749.7659871806</v>
+        <v>495064.3325039586</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>499749.7659871806</v>
+        <v>495064.3325039586</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.1999999999999998</v>
+        <v>0.1999999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2548813.951821815</v>
+        <v>2524917.395894912</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>50065.12188591016</v>
+        <v>49595.73337511718</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>50065.12188591016</v>
+        <v>49595.73337511718</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984632</v>
+        <v>0.0200360761698463</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2600389.776452941</v>
+        <v>2576009.668332323</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>101640.9465170363</v>
+        <v>100688.005812529</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>101640.9465170363</v>
+        <v>100688.005812529</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257613</v>
+        <v>0.04067673601257624</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3065725.777950133</v>
+        <v>3036982.884630293</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>566976.9480142277</v>
+        <v>561661.2221104982</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>566976.9480142277</v>
+        <v>561661.2221104982</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715242</v>
+        <v>0.2269043375715243</v>
       </c>
     </row>
     <row r="31">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3137935.55991226</v>
+        <v>3108515.65951158</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>639186.7299763546</v>
+        <v>633193.9969917852</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>639186.7299763546</v>
+        <v>633193.9969917852</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693045</v>
+        <v>0.2558027130693047</v>
       </c>
     </row>
     <row r="32">
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3630887.684235245</v>
+        <v>3596846.082042737</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1132138.85429934</v>
+        <v>1121524.419522943</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1132138.85429934</v>
+        <v>1121524.419522943</v>
       </c>
       <c r="F32" s="44" t="n">
         <v>0.453082294921327</v>

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-08-04 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-08-10 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>332196</v>
+        <v>348091</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2475321.662519794</v>
+        <v>2593761.492697618</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3108515.65951158</v>
+        <v>3257252.719584358</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>221464</v>
+        <v>232060.6666666667</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>246071.1111111111</v>
+        <v>257845.1851851852</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3065289.684154402</v>
+        <v>3211958.456594871</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3310512.858886754</v>
+        <v>3468915.133122461</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>245223.1747323521</v>
+        <v>256956.6765275896</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>245223.1747323521</v>
+        <v>256956.6765275896</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999996</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3321960</v>
+        <v>3480910</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>256670.3158455985</v>
+        <v>268951.5434051286</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>256670.3158455985</v>
+        <v>268951.5434051286</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004442</v>
+        <v>0.08373444023004431</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3278294.516858215</v>
+        <v>3435155.199543922</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>213004.8327038134</v>
+        <v>223196.7429490509</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>213004.8327038134</v>
+        <v>223196.7429490509</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062575</v>
+        <v>0.06948929943062553</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3137853.820589964</v>
+        <v>3287994.660570811</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>72564.13643556274</v>
+        <v>76036.20397594012</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>72564.13643556274</v>
+        <v>76036.20397594012</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123625</v>
+        <v>0.02367284789123618</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3065289.684154402</v>
+        <v>3211958.456594871</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3065289.684154402</v>
+        <v>3211958.456594871</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3065289.684154402</v>
+        <v>3211958.456594871</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3540558.078206872</v>
+        <v>3709967.615507436</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>475268.3940524706</v>
+        <v>498009.1589125651</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>475268.3940524706</v>
+        <v>498009.1589125651</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850758</v>
+        <v>0.1550484433850757</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2475321.662519794</v>
+        <v>2593761.492697618</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2733284.596167264</v>
+        <v>2864067.503415029</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>257962.9336474692</v>
+        <v>270306.0107174115</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>257962.9336474692</v>
+        <v>270306.0107174115</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>0.104213903814372</v>
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>2919833.411496529</v>
+        <v>3059542.354637739</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>444511.7489767349</v>
+        <v>465780.8619401213</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>444511.7489767349</v>
+        <v>465780.8619401213</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.1795773679466922</v>
+        <v>0.179577367946692</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2750357.402799771</v>
+        <v>2881957.214108464</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>275035.7402799767</v>
+        <v>288195.7214108463</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>275035.7402799767</v>
+        <v>288195.7214108463</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111109</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>2970385.995023753</v>
+        <v>3112513.791237141</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>495064.3325039586</v>
+        <v>518752.2985395235</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>495064.3325039586</v>
+        <v>518752.2985395235</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.1999999999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2524917.395894912</v>
+        <v>2645730.295531721</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>49595.73337511718</v>
+        <v>51968.80283410382</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>49595.73337511718</v>
+        <v>51968.80283410382</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.0200360761698463</v>
+        <v>0.02003607616984635</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2576009.668332323</v>
+        <v>2699267.244215664</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>100688.005812529</v>
+        <v>105505.7515180465</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>100688.005812529</v>
+        <v>105505.7515180465</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257624</v>
+        <v>0.04067673601257616</v>
       </c>
     </row>
     <row r="30">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3036982.884630293</v>
+        <v>3182297.226016698</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>561661.2221104982</v>
+        <v>588535.7333190809</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>561661.2221104982</v>
+        <v>588535.7333190809</v>
       </c>
       <c r="F30" s="44" t="n">
         <v>0.2269043375715243</v>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3108515.65951158</v>
+        <v>3257252.719584358</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>633193.9969917852</v>
+        <v>663491.2268867404</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>633193.9969917852</v>
+        <v>663491.2268867404</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.2558027130693047</v>
+        <v>0.2558027130693048</v>
       </c>
     </row>
     <row r="32">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3596846.082042737</v>
+        <v>3768948.902287621</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1121524.419522943</v>
+        <v>1175187.409590004</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1121524.419522943</v>
+        <v>1175187.409590004</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.453082294921327</v>
+        <v>0.4530822949213271</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-08-10 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-08-14 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>348091</v>
+        <v>351218</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2593761.492697618</v>
+        <v>2617061.986498564</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3257252.719584358</v>
+        <v>3286513.542915442</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>232060.6666666667</v>
+        <v>234145.3333333333</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>257845.1851851852</v>
+        <v>260161.4814814815</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3211958.456594871</v>
+        <v>3240812.388738397</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3468915.133122461</v>
+        <v>3500077.37983747</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>256956.6765275896</v>
+        <v>259264.9910990726</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>256956.6765275896</v>
+        <v>259264.9910990726</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.07999999999999996</v>
+        <v>0.08000000000000027</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3480910</v>
+        <v>3512180</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>268951.5434051286</v>
+        <v>271367.6112616034</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>268951.5434051286</v>
+        <v>271367.6112616034</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004431</v>
+        <v>0.08373444023004462</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3435155.199543922</v>
+        <v>3466014.171217921</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>223196.7429490509</v>
+        <v>225201.7824795237</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>223196.7429490509</v>
+        <v>225201.7824795237</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062553</v>
+        <v>0.06948929943062566</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3287994.660570811</v>
+        <v>3317531.647461035</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>76036.20397594012</v>
+        <v>76719.25872263825</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>76036.20397594012</v>
+        <v>76719.25872263825</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.02367284789123618</v>
+        <v>0.0236728478912363</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3211958.456594871</v>
+        <v>3240812.388738397</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3211958.456594871</v>
+        <v>3240812.388738397</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3211958.456594871</v>
+        <v>3240812.388738397</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3709967.615507436</v>
+        <v>3743295.304915355</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>498009.1589125651</v>
+        <v>502482.916176958</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>498009.1589125651</v>
+        <v>502482.916176958</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850757</v>
+        <v>0.1550484433850759</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2593761.492697618</v>
+        <v>2617061.986498564</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2864067.503415029</v>
+        <v>2889796.232635775</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>270306.0107174115</v>
+        <v>272734.2461372106</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>270306.0107174115</v>
+        <v>272734.2461372106</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>0.104213903814372</v>
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3059542.354637739</v>
+        <v>3087027.089787318</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>465780.8619401213</v>
+        <v>469965.1032887539</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>465780.8619401213</v>
+        <v>469965.1032887539</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.179577367946692</v>
+        <v>0.1795773679466922</v>
       </c>
     </row>
     <row r="26">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2881957.214108464</v>
+        <v>2907846.651665071</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>288195.7214108463</v>
+        <v>290784.665166507</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>288195.7214108463</v>
+        <v>290784.665166507</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3112513.791237141</v>
+        <v>3140474.383798277</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>518752.2985395235</v>
+        <v>523412.397299713</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>518752.2985395235</v>
+        <v>523412.397299713</v>
       </c>
       <c r="F27" s="44" t="n">
         <v>0.2</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2645730.295531721</v>
+        <v>2669497.639801259</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>51968.80283410382</v>
+        <v>52435.65330269467</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>51968.80283410382</v>
+        <v>52435.65330269467</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984635</v>
+        <v>0.02003607616984636</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2699267.244215664</v>
+        <v>2723515.526051915</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>105505.7515180465</v>
+        <v>106453.5395533508</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>105505.7515180465</v>
+        <v>106453.5395533508</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257616</v>
+        <v>0.04067673601257635</v>
       </c>
     </row>
     <row r="30">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3182297.226016698</v>
+        <v>3210884.702928639</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>588535.7333190809</v>
+        <v>593822.7164300745</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>588535.7333190809</v>
+        <v>593822.7164300745</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.2269043375715243</v>
+        <v>0.2269043375715244</v>
       </c>
     </row>
     <row r="31">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3257252.719584358</v>
+        <v>3286513.542915442</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>663491.2268867404</v>
+        <v>669451.5564168771</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>663491.2268867404</v>
+        <v>669451.5564168771</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693048</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3768948.902287621</v>
+        <v>3802806.437292702</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1175187.409590004</v>
+        <v>1185744.450794137</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1175187.409590004</v>
+        <v>1185744.450794137</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213271</v>
+        <v>0.4530822949213272</v>
       </c>
     </row>
     <row r="35">

--- a/Casa_Yano_Loan_Evaluator.xlsx
+++ b/Casa_Yano_Loan_Evaluator.xlsx
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built from 2026-08-14 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
+          <t>Built from 2026-08-24 pro forma. Blue cells are inputs - adjust to test scenarios.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>351218</v>
+        <v>357043</v>
       </c>
     </row>
     <row r="7">
@@ -1912,10 +1912,10 @@
         <v>2800000</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2617061.986498564</v>
+        <v>2660466.328164863</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3286513.542915442</v>
+        <v>3341020.832938967</v>
       </c>
     </row>
     <row r="7">
@@ -2056,10 +2056,10 @@
         <v>224774.5505662314</v>
       </c>
       <c r="D15" s="37" t="n">
-        <v>234145.3333333333</v>
+        <v>238028.6666666667</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>260161.4814814815</v>
+        <v>264476.2962962963</v>
       </c>
     </row>
     <row r="16">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C8" s="26" t="n">
-        <v>3240812.388738397</v>
+        <v>3294561.718682766</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3500077.37983747</v>
+        <v>3558126.656177388</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>259264.9910990726</v>
+        <v>263564.9374946216</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>259264.9910990726</v>
+        <v>263564.9374946216</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>0.08000000000000027</v>
+        <v>0.0800000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>3512180</v>
+        <v>3570430</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>271367.6112616034</v>
+        <v>275868.281317234</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>271367.6112616034</v>
+        <v>275868.281317234</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>0.08373444023004462</v>
+        <v>0.08373444023004428</v>
       </c>
     </row>
     <row r="11">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>3466014.171217921</v>
+        <v>3523498.504444989</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>225201.7824795237</v>
+        <v>228936.7857622234</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>225201.7824795237</v>
+        <v>228936.7857622234</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>0.06948929943062566</v>
+        <v>0.06948929943062565</v>
       </c>
     </row>
     <row r="12">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3317531.647461035</v>
+        <v>3372553.377117433</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>76719.25872263825</v>
+        <v>77991.65843466669</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>76719.25872263825</v>
+        <v>77991.65843466669</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>0.0236728478912363</v>
+        <v>0.02367284789123616</v>
       </c>
     </row>
     <row r="13">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3240812.388738397</v>
+        <v>3294561.718682766</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>3240812.388738397</v>
+        <v>3294561.718682766</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3240812.388738397</v>
+        <v>3294561.718682766</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>3743295.304915355</v>
+        <v>3805378.384800589</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>502482.916176958</v>
+        <v>510816.6661178228</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>502482.916176958</v>
+        <v>510816.6661178228</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>0.1550484433850759</v>
+        <v>0.1550484433850758</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2617061.986498564</v>
+        <v>2660466.328164863</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>2889796.232635775</v>
+        <v>2937723.910189612</v>
       </c>
       <c r="D24" s="42" t="n">
-        <v>272734.2461372106</v>
+        <v>277257.5820247484</v>
       </c>
       <c r="E24" s="43" t="n">
-        <v>272734.2461372106</v>
+        <v>277257.5820247484</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>0.104213903814372</v>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3087027.089787318</v>
+        <v>3138225.86888751</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>469965.1032887539</v>
+        <v>477759.5407226468</v>
       </c>
       <c r="E25" s="43" t="n">
-        <v>469965.1032887539</v>
+        <v>477759.5407226468</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>0.1795773679466922</v>
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>2907846.651665071</v>
+        <v>2956073.697960959</v>
       </c>
       <c r="D26" s="42" t="n">
-        <v>290784.665166507</v>
+        <v>295607.3697960959</v>
       </c>
       <c r="E26" s="43" t="n">
-        <v>290784.665166507</v>
+        <v>295607.3697960959</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.111111111111111</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="27">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3140474.383798277</v>
+        <v>3192559.593797836</v>
       </c>
       <c r="D27" s="42" t="n">
-        <v>523412.397299713</v>
+        <v>532093.2656329731</v>
       </c>
       <c r="E27" s="43" t="n">
-        <v>523412.397299713</v>
+        <v>532093.2656329731</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.2</v>
+        <v>0.2000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>2669497.639801259</v>
+        <v>2713771.634163286</v>
       </c>
       <c r="D28" s="42" t="n">
-        <v>52435.65330269467</v>
+        <v>53305.30599842221</v>
       </c>
       <c r="E28" s="43" t="n">
-        <v>52435.65330269467</v>
+        <v>53305.30599842221</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.02003607616984636</v>
+        <v>0.02003607616984619</v>
       </c>
     </row>
     <row r="29">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>2723515.526051915</v>
+        <v>2768685.414665974</v>
       </c>
       <c r="D29" s="42" t="n">
-        <v>106453.5395533508</v>
+        <v>108219.0865011103</v>
       </c>
       <c r="E29" s="43" t="n">
-        <v>106453.5395533508</v>
+        <v>108219.0865011103</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.04067673601257635</v>
+        <v>0.04067673601257631</v>
       </c>
     </row>
     <row r="30">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3210884.702928639</v>
+        <v>3264137.677988457</v>
       </c>
       <c r="D30" s="42" t="n">
-        <v>593822.7164300745</v>
+        <v>603671.3498235941</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>593822.7164300745</v>
+        <v>603671.3498235941</v>
       </c>
       <c r="F30" s="44" t="n">
         <v>0.2269043375715244</v>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3286513.542915442</v>
+        <v>3341020.832938967</v>
       </c>
       <c r="D31" s="42" t="n">
-        <v>669451.5564168771</v>
+        <v>680554.5047741034</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>669451.5564168771</v>
+        <v>680554.5047741034</v>
       </c>
       <c r="F31" s="44" t="n">
         <v>0.2558027130693048</v>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3802806.437292702</v>
+        <v>3865876.517690717</v>
       </c>
       <c r="D32" s="42" t="n">
-        <v>1185744.450794137</v>
+        <v>1205410.189525853</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>1185744.450794137</v>
+        <v>1205410.189525853</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.4530822949213272</v>
+        <v>0.4530822949213273</v>
       </c>
     </row>
     <row r="35">
